--- a/data/50001533 - GESVIAL.xlsx
+++ b/data/50001533 - GESVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="275">
   <si>
     <t xml:space="preserve"> 50001533 - GESVIAL</t>
   </si>
@@ -918,6 +918,9 @@
   </si>
   <si>
     <t>nicolas.tello@zitron.com</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1213964538804294</t>
@@ -5818,7 +5821,7 @@
         <v>46251.95225530093</v>
       </c>
       <c r="D74" s="5">
-        <v>46251.95227454861</v>
+        <v>46279.12895334491</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>269</v>
@@ -5865,8 +5868,8 @@
       <c r="S74" s="6">
         <v>1</v>
       </c>
-      <c r="T74" s="10" t="s">
-        <v>32</v>
+      <c r="T74" s="12" t="s">
+        <v>272</v>
       </c>
       <c r="U74" s="10" t="s">
         <v>33</v>
@@ -5874,7 +5877,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B75" s="8">
         <v>46118.66251259259</v>
@@ -5883,10 +5886,10 @@
         <v>46251.952265555556</v>
       </c>
       <c r="D75" s="8">
-        <v>46251.95228457176</v>
+        <v>46279.12895329861</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5930,8 +5933,8 @@
       <c r="S75" s="9">
         <v>1</v>
       </c>
-      <c r="T75" s="10" t="s">
-        <v>32</v>
+      <c r="T75" s="12" t="s">
+        <v>272</v>
       </c>
       <c r="U75" s="10" t="s">
         <v>33</v>
